--- a/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/7mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/7mps_analysis.xlsx
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>747.1539659980614</v>
+        <v>747.3302396718793</v>
       </c>
       <c r="Y3">
         <v>0.24137027</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>24.31127313296987</v>
+        <v>24.31107184246338</v>
       </c>
       <c r="Y5">
         <v>0.241191314</v>
@@ -961,7 +961,7 @@
         <v>740.914488871016</v>
       </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
         <v>0.241122778</v>
@@ -1047,7 +1047,7 @@
         <v>743.3458437174781</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
         <v>0.240990468</v>
